--- a/artfynd/A 47907-2023 artfynd.xlsx
+++ b/artfynd/A 47907-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47907-2023 artfynd.xlsx
+++ b/artfynd/A 47907-2023 artfynd.xlsx
@@ -3623,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119510346</v>
+        <v>119510380</v>
       </c>
       <c r="B25" t="n">
-        <v>89288</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3639,21 +3639,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6292</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulgrön kantmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma viridilutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509591</v>
+        <v>509757</v>
       </c>
       <c r="R25" t="n">
-        <v>6675493</v>
+        <v>6675863</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3724,22 +3724,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3757,10 +3762,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119510380</v>
+        <v>119510346</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>89288</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3773,21 +3778,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gulgrön kantmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma viridilutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509757</v>
+        <v>509591</v>
       </c>
       <c r="R26" t="n">
-        <v>6675863</v>
+        <v>6675493</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3858,27 +3863,22 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Lågörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
+          <t>Blåbärsgranskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
